--- a/data/comunus/sinistres.xlsx
+++ b/data/comunus/sinistres.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSQuorum\QuorumTmp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EDC1FF-6D38-4AA0-98D7-6EB2D4865635}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="1000" windowWidth="15000" windowHeight="10000"/>
+    <workbookView xWindow="1005" yWindow="1005" windowWidth="15000" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISTE DES SINISTRES" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
   <si>
     <t>selon AMS, un refoulement des égouts</t>
   </si>
@@ -29,6 +35,9 @@
   </si>
   <si>
     <t>locataire</t>
+  </si>
+  <si>
+    <t>Sinistre</t>
   </si>
   <si>
     <t>AXA WINTERTHUR ASSURANCES SA</t>
@@ -139,13 +148,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,###,##0"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -158,7 +170,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border outline="0">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -169,17 +181,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -467,398 +488,431 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.4375" customWidth="1"/>
-    <col min="2" max="2" width="82.265625" customWidth="1"/>
-    <col min="3" max="3" width="15.8203125" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="82.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="82.265625" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
-    <col min="7" max="7" width="40.078125" customWidth="1"/>
-    <col min="8" max="8" width="31.640625" customWidth="1"/>
-    <col min="9" max="9" width="22.1484375" customWidth="1"/>
-    <col min="10" max="10" width="28.4765625" customWidth="1"/>
-    <col min="11" max="11" width="22.1484375" customWidth="1"/>
-    <col min="12" max="12" width="20.0390625" customWidth="1"/>
-    <col min="13" max="13" width="7.3828125" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625"/>
+    <col min="5" max="5" width="82.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="40.140625" customWidth="1"/>
+    <col min="8" max="8" width="31.5703125" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" customWidth="1"/>
+    <col min="10" max="10" width="28.42578125" customWidth="1"/>
+    <col min="11" max="11" width="22.140625" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3">
+        <v>44538</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3">
+        <v>44587</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3">
+        <v>44587</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>20220001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3">
+        <v>45958</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46072</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>20260001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D4" s="3">
+        <v>45953</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46070</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46070</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>20260002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46049</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46095</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>20260007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>45951</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46073</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>20260003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="D7" s="3">
+        <v>41953</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="3">
+        <v>41975</v>
+      </c>
+      <c r="H7" s="3">
+        <v>41953</v>
+      </c>
+      <c r="I7" s="3">
+        <v>41974</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>20140003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="3">
+        <v>45755</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46084</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>20260005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46050</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46095</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>20260006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>42069</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3">
+        <v>42069</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>20150001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D13" s="3">
+        <v>46071</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>20260004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2">
-        <v>44538</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="2">
-        <v>44587</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="2">
-        <v>44587</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="2">
-        <v>45958</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46072</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2">
-        <v>45953</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46070</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>46070</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46049</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>46095</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2">
-        <v>45951</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2">
-        <v>46073</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2">
-        <v>41953</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2">
-        <v>41975</v>
-      </c>
-      <c r="H7" s="2">
-        <v>41953</v>
-      </c>
-      <c r="I7" s="2">
-        <v>41974</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2">
-        <v>45755</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2">
-        <v>46084</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46050</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="2">
-        <v>46095</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="E10" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>42069</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="2">
-        <v>42069</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="D13" s="2">
-        <v>46071</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>46087</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>46090</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>20260008</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection/>
-  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9"/>
 </worksheet>

--- a/data/comunus/sinistres.xlsx
+++ b/data/comunus/sinistres.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSQuorum\QuorumTmp\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EDC1FF-6D38-4AA0-98D7-6EB2D4865635}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="1005" windowWidth="15000" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="1000" windowWidth="15000" windowHeight="10000"/>
   </bookViews>
   <sheets>
     <sheet name="LISTE DES SINISTRES" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>selon AMS, un refoulement des égouts</t>
   </si>
@@ -28,6 +22,12 @@
     <t>Tentative d'éffraction</t>
   </si>
   <si>
+    <t>Date demande de devis</t>
+  </si>
+  <si>
+    <t>Champreveyres 22</t>
+  </si>
+  <si>
     <t>Dégât d'eau dans la cave numéro 3 de l'immeuble. Sûrement dû au dégât d'eau de</t>
   </si>
   <si>
@@ -37,12 +37,24 @@
     <t>locataire</t>
   </si>
   <si>
+    <t>Malakoff 24</t>
+  </si>
+  <si>
+    <t>PPE Ecoliers 3A</t>
+  </si>
+  <si>
     <t>Sinistre</t>
   </si>
   <si>
+    <t>Vieux-Patriotes 51</t>
+  </si>
+  <si>
     <t>AXA WINTERTHUR ASSURANCES SA</t>
   </si>
   <si>
+    <t>Rue Pierre de Savoie 7</t>
+  </si>
+  <si>
     <t>la</t>
   </si>
   <si>
@@ -61,9 +73,18 @@
     <t>Partie d'ouvrage touchée</t>
   </si>
   <si>
+    <t>PPE Gabriel-Lory 2</t>
+  </si>
+  <si>
+    <t>PPE Orée 100a - 100b</t>
+  </si>
+  <si>
     <t>Évacuation d'eau suite à l'inondation des caves, nettoyages locaux communs sui</t>
   </si>
   <si>
+    <t>Locle 23</t>
+  </si>
+  <si>
     <t>date déclaration</t>
   </si>
   <si>
@@ -124,6 +145,9 @@
     <t>Supposition d'un dégât d'eau à l'étage du dessus de l'appartement lésé, il y a</t>
   </si>
   <si>
+    <t>26 Mars 36</t>
+  </si>
+  <si>
     <t>Logement de 3.5 pièces au 3ème étage - M. Adis Kuljancic - Infiltration d'eau</t>
   </si>
   <si>
@@ -133,10 +157,19 @@
     <t>020 002</t>
   </si>
   <si>
+    <t>Bois-Noir 38</t>
+  </si>
+  <si>
     <t>Suite vandalisme, la porte de l'immeuble a été fissurée.</t>
   </si>
   <si>
     <t>Assurance Date du rbt</t>
+  </si>
+  <si>
+    <t>Crêt 93 - BF 3419</t>
+  </si>
+  <si>
+    <t>Nom immeuble</t>
   </si>
   <si>
     <t>Agencement de la cuisine + sol</t>
@@ -148,16 +181,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,##0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -170,7 +203,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border outline="0">
       <left/>
       <right/>
       <top/>
@@ -183,24 +216,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -488,431 +513,499 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="82.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="82.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="40.140625" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" customWidth="1"/>
-    <col min="10" max="10" width="28.42578125" customWidth="1"/>
-    <col min="11" max="11" width="22.140625" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="7.42578125" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.203125" customWidth="1"/>
+    <col min="2" max="2" width="8.4375" customWidth="1"/>
+    <col min="3" max="3" width="82.265625" customWidth="1"/>
+    <col min="4" max="4" width="15.8203125" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="82.265625" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="40.078125" customWidth="1"/>
+    <col min="9" max="9" width="22.1484375" customWidth="1"/>
+    <col min="10" max="10" width="31.640625" customWidth="1"/>
+    <col min="11" max="11" width="22.1484375" customWidth="1"/>
+    <col min="12" max="12" width="28.4765625" customWidth="1"/>
+    <col min="13" max="13" width="22.1484375" customWidth="1"/>
+    <col min="14" max="14" width="20.0390625" customWidth="1"/>
+    <col min="15" max="15" width="7.3828125" customWidth="1"/>
+    <col min="16" max="16" width="8.4375" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2">
+        <v>44538</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2">
+        <v>44587</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="2">
+        <v>44579</v>
+      </c>
+      <c r="J2" s="2">
+        <v>44587</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>20220001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45958</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46072</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2">
+        <v>45982</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>20260001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45953</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46070</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2">
+        <v>45953</v>
+      </c>
+      <c r="J4" s="2">
+        <v>46070</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>20260002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46049</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>46095</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>20260007</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E6" s="2">
+        <v>45951</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2">
+        <v>46073</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="2">
+        <v>46073</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>20260003</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2">
+        <v>41953</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="2">
+        <v>41975</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="2">
+        <v>41953</v>
+      </c>
+      <c r="K7" s="2">
+        <v>41974</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4">
+        <v>20140003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E8" s="2">
+        <v>45755</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2">
+        <v>46084</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="2">
+        <v>46084</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4">
+        <v>20260005</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46050</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46095</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="2">
+        <v>46095</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4">
+        <v>20260006</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>42069</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="2">
+        <v>42069</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4">
+        <v>20150001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="E13" s="2">
+        <v>46071</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4">
+        <v>20260004</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="3">
-        <v>44538</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="3">
-        <v>44587</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="3">
-        <v>44587</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
-      <c r="N2" s="1">
-        <v>20220001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="3">
-        <v>45958</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="3">
-        <v>46072</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>20260001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3">
-        <v>45953</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="3">
-        <v>46070</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46070</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>20260002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="3">
-        <v>46049</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>46095</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>20260007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="3">
-        <v>45951</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3">
-        <v>46073</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>20260003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="3">
-        <v>41953</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="3">
-        <v>41975</v>
-      </c>
-      <c r="H7" s="3">
-        <v>41953</v>
-      </c>
-      <c r="I7" s="3">
-        <v>41974</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="1">
-        <v>20140003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="3">
-        <v>45755</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="3">
-        <v>46084</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>20260005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3">
-        <v>46050</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>46095</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>20260006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3">
-        <v>42069</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3">
-        <v>42069</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>20150001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D13" s="3">
-        <v>46071</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>20260004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="E14" s="2">
         <v>46087</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="2">
         <v>46090</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1"/>
       <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4">
         <v>20260008</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection/>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9"/>
 </worksheet>

--- a/data/comunus/sinistres.xlsx
+++ b/data/comunus/sinistres.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="75">
   <si>
     <t>selon AMS, un refoulement des égouts</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Vieux-Patriotes 51</t>
   </si>
   <si>
+    <t>Moulins 28</t>
+  </si>
+  <si>
     <t>AXA WINTERTHUR ASSURANCES SA</t>
   </si>
   <si>
@@ -58,9 +61,15 @@
     <t>la</t>
   </si>
   <si>
+    <t>Mur de la buanderie humide et salit de moisissures + joint de la tablette de f</t>
+  </si>
+  <si>
     <t>Tâches sèches sur le plafond de l'appartement lésé.</t>
   </si>
   <si>
+    <t>PPE Gabriel-Lory 2 - 4</t>
+  </si>
+  <si>
     <t>Assurance montant remboursé</t>
   </si>
   <si>
@@ -76,6 +85,12 @@
     <t>PPE Gabriel-Lory 2</t>
   </si>
   <si>
+    <t>Dynactif SA</t>
+  </si>
+  <si>
+    <t>Vauthier Roland</t>
+  </si>
+  <si>
     <t>PPE Orée 100a - 100b</t>
   </si>
   <si>
@@ -85,12 +100,18 @@
     <t>Locle 23</t>
   </si>
   <si>
+    <t>Comunus SICAV</t>
+  </si>
+  <si>
     <t>date déclaration</t>
   </si>
   <si>
     <t>GRIESSEN Fabien</t>
   </si>
   <si>
+    <t>Nom juridique 1</t>
+  </si>
+  <si>
     <t>infiltration dans la cage d'escaliers + moisissure</t>
   </si>
   <si>
@@ -109,9 +130,27 @@
     <t>Refoulement d'eau par l'évier de la cuisine</t>
   </si>
   <si>
+    <t>Soleil 13</t>
+  </si>
+  <si>
+    <t>Mme Aicha HAFEZ et M. Magdy HAFEZ</t>
+  </si>
+  <si>
+    <t>Infiltration d'eau par la tablette de fenêtre du locataire habitant au-dessus</t>
+  </si>
+  <si>
+    <t>STARVAL SA</t>
+  </si>
+  <si>
     <t>ECAP</t>
   </si>
   <si>
+    <t>Cause encore à déterminer mais supposition d'une fuite provenant du WC de chez</t>
+  </si>
+  <si>
+    <t>Saules 14</t>
+  </si>
+  <si>
     <t>date sinistre</t>
   </si>
   <si>
@@ -127,12 +166,18 @@
     <t>Cage d'escalier Malakoff 24 présence de poches d'eau au rez et au 1er étage, i</t>
   </si>
   <si>
+    <t>Parquet stratifié gonflé. Plafond salon de la locataire en dessous endommagés</t>
+  </si>
+  <si>
     <t>Assurance Date Accord</t>
   </si>
   <si>
     <t>Récente fonte de neige</t>
   </si>
   <si>
+    <t>Fuite d'eau chez la voisine lorsque le locataire prend des douches.</t>
+  </si>
+  <si>
     <t>Facturé</t>
   </si>
   <si>
@@ -142,15 +187,18 @@
     <t>Assurance Franchise</t>
   </si>
   <si>
+    <t>Logement de 3.5 pièces au 3ème étage - M. Adis Kuljancic + dégâts consécutifs</t>
+  </si>
+  <si>
     <t>Supposition d'un dégât d'eau à l'étage du dessus de l'appartement lésé, il y a</t>
   </si>
   <si>
+    <t>Société coopérative de construction et</t>
+  </si>
+  <si>
     <t>26 Mars 36</t>
   </si>
   <si>
-    <t>Logement de 3.5 pièces au 3ème étage - M. Adis Kuljancic - Infiltration d'eau</t>
-  </si>
-  <si>
     <t>Travaux de surélévation de l'immeuble.</t>
   </si>
   <si>
@@ -163,19 +211,34 @@
     <t>Suite vandalisme, la porte de l'immeuble a été fissurée.</t>
   </si>
   <si>
+    <t>Gendre Jean-Philippe &amp; Marie-Claude</t>
+  </si>
+  <si>
     <t>Assurance Date du rbt</t>
   </si>
   <si>
     <t>Crêt 93 - BF 3419</t>
   </si>
   <si>
+    <t>Vauthier Roland &amp; Fischer Bernard</t>
+  </si>
+  <si>
     <t>Nom immeuble</t>
   </si>
   <si>
     <t>Agencement de la cuisine + sol</t>
   </si>
   <si>
+    <t>Fuite d'eau.</t>
+  </si>
+  <si>
     <t>Date envoi devis à l'assurance</t>
+  </si>
+  <si>
+    <t>VAUDOISE ASSURANCES</t>
+  </si>
+  <si>
+    <t>S.I. Beau-Parc A S.A.</t>
   </si>
 </sst>
 </file>
@@ -217,9 +280,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +581,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.203125" customWidth="1"/>
@@ -537,57 +600,61 @@
     <col min="14" max="14" width="20.0390625" customWidth="1"/>
     <col min="15" max="15" width="7.3828125" customWidth="1"/>
     <col min="16" max="16" width="8.4375" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625"/>
+    <col min="17" max="17" width="40.078125" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>9</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2">
@@ -595,24 +662,24 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="2">
+        <v>33</v>
+      </c>
+      <c r="E2" s="4">
         <v>44538</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="2">
+        <v>49</v>
+      </c>
+      <c r="G2" s="4">
         <v>44587</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="2">
+        <v>48</v>
+      </c>
+      <c r="I2" s="4">
         <v>44579</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="4">
         <v>44587</v>
       </c>
       <c r="K2" s="1"/>
@@ -626,8 +693,11 @@
       <c r="O2" s="1">
         <v>0</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="2">
         <v>20220001</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -635,21 +705,21 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="2">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4">
         <v>45958</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46072</v>
+        <v>57</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46142</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="2">
+        <v>12</v>
+      </c>
+      <c r="I3" s="4">
         <v>45982</v>
       </c>
       <c r="J3" s="1"/>
@@ -664,33 +734,36 @@
       <c r="O3" s="1">
         <v>0</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="2">
         <v>20260001</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4">
         <v>45953</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="2">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4">
         <v>46070</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="2">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4">
         <v>45953</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="4">
         <v>46070</v>
       </c>
       <c r="K4" s="1"/>
@@ -704,28 +777,31 @@
       <c r="O4" s="1">
         <v>0</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="2">
         <v>20260002</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4">
         <v>46049</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="4">
         <v>46095</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -740,8 +816,11 @@
       <c r="O5" s="1">
         <v>0</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="2">
         <v>20260007</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -749,27 +828,27 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="2">
+        <v>30</v>
+      </c>
+      <c r="E6" s="4">
         <v>45951</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="2">
+        <v>37</v>
+      </c>
+      <c r="G6" s="4">
         <v>46073</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="2">
+        <v>12</v>
+      </c>
+      <c r="I6" s="4">
         <v>46073</v>
       </c>
       <c r="J6" s="1"/>
@@ -784,31 +863,34 @@
       <c r="O6" s="1">
         <v>0</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="2">
         <v>20260003</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4">
         <v>41953</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="2">
+        <v>61</v>
+      </c>
+      <c r="G7" s="4">
         <v>41975</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="2">
+      <c r="J7" s="4">
         <v>41953</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="4">
         <v>41974</v>
       </c>
       <c r="L7" s="1">
@@ -821,30 +903,33 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="2">
         <v>20140003</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4">
         <v>45755</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="2">
+        <v>58</v>
+      </c>
+      <c r="G8" s="4">
         <v>46084</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="2">
+        <v>48</v>
+      </c>
+      <c r="I8" s="4">
         <v>46084</v>
       </c>
       <c r="J8" s="1"/>
@@ -859,32 +944,33 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="2">
         <v>20260005</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46050</v>
+        <v>50</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46110</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="2">
-        <v>46095</v>
+        <v>43</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46127</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="2">
-        <v>46095</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1">
@@ -897,33 +983,73 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="4">
-        <v>20260006</v>
+      <c r="P9" s="2">
+        <v>20260009</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46079</v>
+      </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46127</v>
+      </c>
+      <c r="I10" s="4">
+        <v>46079</v>
+      </c>
+      <c r="J10" s="4">
+        <v>46112</v>
+      </c>
+      <c r="K10" s="4">
+        <v>46122</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="2">
+        <v>20260010</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="2">
-        <v>42069</v>
+        <v>15</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46065</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="2">
-        <v>42069</v>
+        <v>40</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46135</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -938,53 +1064,77 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="4">
-        <v>20150001</v>
+      <c r="P11" s="2">
+        <v>20260011</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46050</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46095</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="4">
+        <v>46095</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2">
+        <v>20260006</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2">
-        <v>46071</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4">
-        <v>20260004</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="2">
-        <v>46087</v>
+        <v>5</v>
+      </c>
+      <c r="E14" s="4">
+        <v>42069</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>46090</v>
+        <v>52</v>
+      </c>
+      <c r="G14" s="4">
+        <v>42069</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -999,8 +1149,75 @@
       <c r="O14" s="1">
         <v>0</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P14" s="2">
+        <v>20150001</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4">
+        <v>46071</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="2">
+        <v>20260004</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46087</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46090</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="2">
         <v>20260008</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
